--- a/mock planning.xlsx
+++ b/mock planning.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t xml:space="preserve">off-(s+g)</t>
   </si>
@@ -124,6 +124,33 @@
   </si>
   <si>
     <t xml:space="preserve">15%(4+3) = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left from -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right from 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From -1 to 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To -3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From -1 to 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To -4</t>
   </si>
 </sst>
 </file>
@@ -492,7 +519,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AL36"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1024,8 +1051,12 @@
       <c r="W11" s="8" t="n">
         <v>-6</v>
       </c>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
+      <c r="X11" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y11" s="8" t="n">
+        <v>-4</v>
+      </c>
       <c r="Z11" s="5"/>
       <c r="AA11" s="5"/>
       <c r="AB11" s="5"/>
@@ -1257,6 +1288,74 @@
         <v>20</v>
       </c>
     </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/mock planning.xlsx
+++ b/mock planning.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t xml:space="preserve">off-(s+g)</t>
   </si>
@@ -144,10 +144,10 @@
     <t xml:space="preserve">From -1 to 15</t>
   </si>
   <si>
+    <t xml:space="preserve">From -1 to 21</t>
+  </si>
+  <si>
     <t xml:space="preserve">To -3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From -1 to 21</t>
   </si>
   <si>
     <t xml:space="preserve">To -4</t>
@@ -519,7 +519,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AL36"/>
+  <dimension ref="A1:AL39"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -836,101 +836,93 @@
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8" t="n">
-        <v>-6</v>
-      </c>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
-      <c r="AG7" s="4"/>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
+      <c r="A8" s="10" t="s">
+        <v>0</v>
+      </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="M8" s="5"/>
       <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
+      <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
+      <c r="T8" s="5"/>
       <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8" t="n">
+        <v>-6</v>
+      </c>
       <c r="X8" s="8"/>
       <c r="Y8" s="8"/>
       <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
+      <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
@@ -941,48 +933,34 @@
       <c r="AI8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>20</v>
-      </c>
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="8"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
+      <c r="N9" s="5"/>
       <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
+      <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
       <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
+      <c r="U9" s="5"/>
       <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
+      <c r="W9" s="8"/>
       <c r="X9" s="8"/>
       <c r="Y9" s="8"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
+      <c r="AB9" s="5"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
@@ -992,367 +970,483 @@
       <c r="AI9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="A10" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4"/>
+      <c r="AF10" s="4"/>
+      <c r="AG10" s="4"/>
+      <c r="AH10" s="4"/>
+      <c r="AI10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="6"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="8" t="n">
-        <v>-7</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>-6</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Y11" s="8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
+      <c r="AI11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
       <c r="AA12" s="5"/>
       <c r="AB12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
       <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
       <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="8"/>
+      <c r="V13" s="8" t="n">
+        <v>-7</v>
+      </c>
+      <c r="W13" s="8" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>-5</v>
+      </c>
       <c r="Y13" s="8" t="n">
         <v>-4</v>
       </c>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="8"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
       <c r="AB13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>20</v>
-      </c>
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
       <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
       <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
       <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z14" s="8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AA14" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB14" s="8" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W14" s="8"/>
+      <c r="X14" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
-      <c r="W15" s="5" t="s">
+      <c r="W15" s="5"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z16" s="8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA16" s="8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB16" s="8" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
-      <c r="AB15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="0" t="s">
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G19" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="0" t="s">
+      <c r="H19" s="0" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="0" t="s">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G20" s="0" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="0" t="s">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G21" s="0" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="H24" s="0" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="0" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="C38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C39" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D39" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E39" s="0" t="n">
         <v>4</v>
       </c>
     </row>
